--- a/docs/機能一覧.xlsx
+++ b/docs/機能一覧.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="213">
   <si>
     <t>機能カテゴリ</t>
   </si>
@@ -521,6 +521,12 @@
     <t>ロゴ設定</t>
   </si>
   <si>
+    <t>MVP</t>
+  </si>
+  <si>
+    <t>成長期</t>
+  </si>
+  <si>
     <t>オプション管理</t>
   </si>
   <si>
@@ -531,6 +537,36 @@
   </si>
   <si>
     <t>運営者、利用者権限変更</t>
+  </si>
+  <si>
+    <t>ユーザーアカウント管理</t>
+  </si>
+  <si>
+    <t>プラットフォーム全ユーザー一覧（全テナント横断でのユーザー検索・表示）</t>
+  </si>
+  <si>
+    <t>ユーザー詳細表示（所属コミュニティ・ログイン履歴・活動状況の確認）</t>
+  </si>
+  <si>
+    <t>ユーザーアカウントの停止・凍結（不正利用者のアカウント一時停止）</t>
+  </si>
+  <si>
+    <t>パスワード強制リセット（ユーザーへのリセットメール強制送信）</t>
+  </si>
+  <si>
+    <t>ユーザーのメールアドレス変更（本人確認後の管理者による変更対応）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">代理ログイン機能（サポート目的でのユーザー画面確認）	</t>
+  </si>
+  <si>
+    <t>ユーザー活動ログ閲覧（操作履歴・ログイン履歴の詳細表示）</t>
+  </si>
+  <si>
+    <t>システム設定</t>
+  </si>
+  <si>
+    <t>プラットフォーム基本情報設定（サービス名・URL・ロゴ・利用規約）</t>
   </si>
   <si>
     <t>基本設定</t>
@@ -631,7 +667,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -654,6 +690,11 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF333333"/>
+      <name val="&quot;Helvetica Neue&quot;"/>
     </font>
     <font>
       <color theme="1"/>
@@ -721,7 +762,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -776,7 +817,16 @@
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -15961,7 +16011,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="30.0"/>
-    <col customWidth="1" min="2" max="2" width="74.0"/>
+    <col customWidth="1" min="2" max="2" width="82.57"/>
     <col customWidth="1" min="3" max="3" width="8.0"/>
     <col customWidth="1" min="4" max="4" width="13.29"/>
     <col customWidth="1" min="5" max="5" width="37.14"/>
@@ -15976,10 +16026,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>167</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -16008,10 +16058,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>7</v>
@@ -16021,10 +16071,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>7</v>
@@ -16033,64 +16083,100 @@
       <c r="E3" s="7"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5"/>
+      <c r="A4" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="3"/>
+      <c r="B5" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="15"/>
+      <c r="B6" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="D6" s="15"/>
       <c r="E6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="15"/>
+      <c r="B7" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="D7" s="15"/>
       <c r="E7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="15"/>
+      <c r="B8" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="D8" s="15"/>
       <c r="E8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="B9" s="14" t="s">
+        <v>178</v>
+      </c>
       <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
+      <c r="D9" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+      <c r="B10" s="19" t="s">
+        <v>179</v>
+      </c>
       <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
+      <c r="D10" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="15"/>
+      <c r="A11" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>7</v>
+      </c>
       <c r="D11" s="15"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="3"/>
@@ -22344,117 +22430,117 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="s">
-        <v>170</v>
+      <c r="A1" s="21" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="18" t="s">
-        <v>171</v>
+      <c r="B2" s="21" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="18" t="s">
-        <v>172</v>
+      <c r="B3" s="21" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="18" t="s">
-        <v>173</v>
+      <c r="B4" s="21" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="18" t="s">
-        <v>174</v>
+      <c r="B5" s="21" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="18" t="s">
-        <v>175</v>
+      <c r="B6" s="21" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="18" t="s">
-        <v>176</v>
+      <c r="B7" s="21" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="18" t="s">
-        <v>177</v>
+      <c r="B8" s="21" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="18" t="s">
-        <v>178</v>
+      <c r="B9" s="21" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="21" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="18" t="s">
-        <v>179</v>
+      <c r="B12" s="21" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="18" t="s">
-        <v>180</v>
+      <c r="B13" s="21" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="18" t="s">
-        <v>181</v>
+      <c r="B14" s="21" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="18" t="s">
-        <v>182</v>
+      <c r="B15" s="21" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="18" t="s">
-        <v>183</v>
+      <c r="B16" s="21" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="18" t="s">
-        <v>184</v>
+      <c r="B17" s="21" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="18" t="s">
-        <v>185</v>
+      <c r="B18" s="21" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="18" t="s">
-        <v>186</v>
+      <c r="B19" s="21" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="18" t="s">
-        <v>187</v>
+      <c r="B20" s="21" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="18" t="s">
-        <v>188</v>
+      <c r="B21" s="21" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="18" t="s">
-        <v>189</v>
+      <c r="B22" s="21" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="18" t="s">
-        <v>190</v>
+      <c r="B23" s="21" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18"/>
+      <c r="A25" s="21"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -22472,58 +22558,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="21" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="s">
-        <v>191</v>
+      <c r="A2" s="21" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="s">
-        <v>192</v>
+      <c r="A3" s="21" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="s">
-        <v>193</v>
+      <c r="A4" s="21" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>194</v>
+      <c r="A5" s="21" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="s">
-        <v>195</v>
+      <c r="A6" s="21" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>196</v>
+      <c r="A7" s="21" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="s">
-        <v>197</v>
+      <c r="A8" s="21" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>198</v>
+      <c r="A9" s="21" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="s">
-        <v>199</v>
+      <c r="A10" s="21" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>200</v>
+      <c r="A11" s="21" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/docs/機能一覧.xlsx
+++ b/docs/機能一覧.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="250">
   <si>
     <t>機能カテゴリ</t>
   </si>
@@ -281,6 +281,105 @@
   </si>
   <si>
     <t>コンテンツ一覧</t>
+  </si>
+  <si>
+    <t>プロフィール</t>
+  </si>
+  <si>
+    <t>基本情報編集</t>
+  </si>
+  <si>
+    <t>公開情報編集/プレビュー</t>
+  </si>
+  <si>
+    <t>関心分野編集</t>
+  </si>
+  <si>
+    <t>外国語対応一覧・編集</t>
+  </si>
+  <si>
+    <t>会員証（バーコード）</t>
+  </si>
+  <si>
+    <t>カレンダー</t>
+  </si>
+  <si>
+    <t>カレンダー表示（自分の予定、タスク期限、イベント、コミュニティメンバーの予定）</t>
+  </si>
+  <si>
+    <t>月、週、日で切り替え</t>
+  </si>
+  <si>
+    <t>新規スケジュールを登録</t>
+  </si>
+  <si>
+    <t>メモ</t>
+  </si>
+  <si>
+    <t>メモ作成</t>
+  </si>
+  <si>
+    <t>メモ一覧、検索</t>
+  </si>
+  <si>
+    <t>マイプロジェクト</t>
+  </si>
+  <si>
+    <t>参加しているプロジェクト一覧</t>
+  </si>
+  <si>
+    <t>検索</t>
+  </si>
+  <si>
+    <t>マイライブラリー</t>
+  </si>
+  <si>
+    <t>ライブラリー一覧、属性、統計</t>
+  </si>
+  <si>
+    <t>キーワード検索、詳細検索</t>
+  </si>
+  <si>
+    <t>ライブラリ登録</t>
+  </si>
+  <si>
+    <t>マイチケット</t>
+  </si>
+  <si>
+    <t>チケット一覧</t>
+  </si>
+  <si>
+    <t>チケット詳細</t>
+  </si>
+  <si>
+    <t>マイ予約</t>
+  </si>
+  <si>
+    <t>予約、過去予約一覧、検索</t>
+  </si>
+  <si>
+    <t>スペース詳細</t>
+  </si>
+  <si>
+    <t>マイタスク</t>
+  </si>
+  <si>
+    <t>絞り込み（プロジェクト）</t>
+  </si>
+  <si>
+    <t>自分の設定</t>
+  </si>
+  <si>
+    <t>通知設定</t>
+  </si>
+  <si>
+    <t>ヘルプ</t>
+  </si>
+  <si>
+    <t>よくある質問</t>
+  </si>
+  <si>
+    <t>システム説明</t>
   </si>
   <si>
     <t>イベント作成（タイトル・説明・日時・場所・参加費の設定）</t>
@@ -512,9 +611,6 @@
     <t>メール設定</t>
   </si>
   <si>
-    <t>通知設定</t>
-  </si>
-  <si>
     <t>環境設定</t>
   </si>
   <si>
@@ -661,6 +757,21 @@
   </si>
   <si>
     <t>・メンバー属性はそこでつかわれているのか？</t>
+  </si>
+  <si>
+    <t>・動画はvimeoを使うか？</t>
+  </si>
+  <si>
+    <t>・会員証（バーコード）は何に使っているか？</t>
+  </si>
+  <si>
+    <t>・会費、入会金、定額決済プランなども同じ仕組みか？</t>
+  </si>
+  <si>
+    <t>・来場履歴について、メンバーの詳細ページにある。施設に入退場の記録が残される機能と見受けられるがこの機能も必要か？</t>
+  </si>
+  <si>
+    <t>・ポイントの運用方法</t>
   </si>
 </sst>
 </file>
@@ -692,14 +803,14 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12.0"/>
       <color rgb="FF333333"/>
       <name val="&quot;Helvetica Neue&quot;"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -811,6 +922,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -820,14 +934,11 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1843,191 +1954,319 @@
       <c r="E65" s="3"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="15"/>
+      <c r="A66" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D66" s="15"/>
       <c r="E66" s="3"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="15"/>
+      <c r="B67" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D67" s="15"/>
       <c r="E67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="15"/>
+      <c r="B68" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D68" s="15"/>
       <c r="E68" s="3"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="15"/>
+      <c r="B69" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D69" s="15"/>
       <c r="E69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="15"/>
+      <c r="A70" s="14"/>
+      <c r="B70" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D70" s="15"/>
       <c r="E70" s="3"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="15"/>
+      <c r="A71" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D71" s="15"/>
       <c r="E71" s="3"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="15"/>
+      <c r="B72" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D72" s="15"/>
       <c r="E72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="15"/>
+      <c r="B73" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D73" s="15"/>
       <c r="E73" s="3"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="15"/>
+      <c r="B74" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D74" s="15"/>
       <c r="E74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="15"/>
+      <c r="A75" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D75" s="15"/>
       <c r="E75" s="3"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="15"/>
+      <c r="B76" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D76" s="15"/>
       <c r="E76" s="3"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="15"/>
+      <c r="B77" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D77" s="15"/>
       <c r="E77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="15"/>
+      <c r="A78" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D78" s="15"/>
       <c r="E78" s="3"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="15"/>
+      <c r="B79" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D79" s="15"/>
       <c r="E79" s="3"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="15"/>
+      <c r="A80" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D80" s="15"/>
       <c r="E80" s="3"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="15"/>
+      <c r="B81" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D81" s="15"/>
       <c r="E81" s="3"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="15"/>
+      <c r="B82" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D82" s="15"/>
       <c r="E82" s="3"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="15"/>
+      <c r="A83" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D83" s="15"/>
       <c r="E83" s="3"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="15"/>
+      <c r="B84" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D84" s="15"/>
       <c r="E84" s="3"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="15"/>
+      <c r="A85" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D85" s="15"/>
       <c r="E85" s="3"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="15"/>
+      <c r="B86" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D86" s="15"/>
       <c r="E86" s="3"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="15"/>
+      <c r="A87" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D87" s="15"/>
       <c r="E87" s="3"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="15"/>
+      <c r="B88" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D88" s="15"/>
       <c r="E88" s="3"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="15"/>
+      <c r="A89" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D89" s="15"/>
       <c r="E89" s="3"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="15"/>
+      <c r="B90" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D90" s="15"/>
       <c r="E90" s="3"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="15"/>
+      <c r="A91" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D91" s="15"/>
       <c r="E91" s="3"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="15"/>
+      <c r="B92" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D92" s="15"/>
       <c r="E92" s="3"/>
     </row>
@@ -8547,7 +8786,7 @@
         <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>7</v>
@@ -8558,7 +8797,7 @@
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="5"/>
       <c r="B13" s="7" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>7</v>
@@ -8580,7 +8819,7 @@
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="5"/>
       <c r="B15" s="7" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>7</v>
@@ -8602,7 +8841,7 @@
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="5"/>
       <c r="B17" s="7" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>7</v>
@@ -8613,7 +8852,7 @@
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6" t="s">
@@ -8635,7 +8874,7 @@
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="5"/>
       <c r="B20" s="7" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>7</v>
@@ -8646,7 +8885,7 @@
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="7" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>7</v>
@@ -8657,7 +8896,7 @@
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="5"/>
       <c r="B22" s="7" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>7</v>
@@ -8679,7 +8918,7 @@
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="5"/>
       <c r="B24" s="7" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>7</v>
@@ -8690,7 +8929,7 @@
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="7" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>7</v>
@@ -8712,7 +8951,7 @@
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>7</v>
@@ -8725,7 +8964,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>7</v>
@@ -8736,7 +8975,7 @@
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="5"/>
       <c r="B29" s="7" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>7</v>
@@ -8747,7 +8986,7 @@
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="5"/>
       <c r="B30" s="7" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>7</v>
@@ -8769,7 +9008,7 @@
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="5"/>
       <c r="B32" s="7" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>7</v>
@@ -8791,7 +9030,7 @@
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6" t="s">
@@ -8802,7 +9041,7 @@
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6" t="s">
@@ -8859,7 +9098,7 @@
     <row r="40" ht="18.75" customHeight="1">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>7</v>
@@ -8870,7 +9109,7 @@
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6" t="s">
@@ -8881,7 +9120,7 @@
     <row r="42" ht="18.75" customHeight="1">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6" t="s">
@@ -8892,7 +9131,7 @@
     <row r="43" ht="18.75" customHeight="1">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6" t="s">
@@ -8903,7 +9142,7 @@
     <row r="44" ht="18.75" customHeight="1">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6" t="s">
@@ -8969,7 +9208,7 @@
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" ht="18.75" customHeight="1">
@@ -8986,7 +9225,7 @@
     <row r="51" ht="18.75" customHeight="1">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>7</v>
@@ -8997,7 +9236,7 @@
     <row r="52" ht="18.75" customHeight="1">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>7</v>
@@ -9019,7 +9258,7 @@
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="6" t="s">
@@ -9043,7 +9282,7 @@
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" s="5"/>
       <c r="B56" s="7" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>7</v>
@@ -9054,7 +9293,7 @@
     <row r="57" ht="18.75" customHeight="1">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>7</v>
@@ -9098,7 +9337,7 @@
     <row r="61" ht="18.75" customHeight="1">
       <c r="A61" s="5"/>
       <c r="B61" s="5" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>7</v>
@@ -9109,7 +9348,7 @@
     <row r="62" ht="18.75" customHeight="1">
       <c r="A62" s="5"/>
       <c r="B62" s="7" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>7</v>
@@ -9120,7 +9359,7 @@
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" s="5"/>
       <c r="B63" s="7" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6" t="s">
@@ -9131,7 +9370,7 @@
     <row r="64" ht="18.75" customHeight="1">
       <c r="A64" s="5"/>
       <c r="B64" s="7" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="6" t="s">
@@ -9177,7 +9416,7 @@
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>7</v>
@@ -9188,7 +9427,7 @@
     <row r="69" ht="18.75" customHeight="1">
       <c r="A69" s="5"/>
       <c r="B69" s="5" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>7</v>
@@ -9201,10 +9440,10 @@
         <v>57</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="C70" s="6"/>
-      <c r="D70" s="16" t="s">
+      <c r="D70" s="17" t="s">
         <v>7</v>
       </c>
       <c r="E70" s="5"/>
@@ -9212,10 +9451,10 @@
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" s="5"/>
       <c r="B71" s="5" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="C71" s="6"/>
-      <c r="D71" s="16" t="s">
+      <c r="D71" s="17" t="s">
         <v>7</v>
       </c>
       <c r="E71" s="5"/>
@@ -9226,7 +9465,7 @@
         <v>58</v>
       </c>
       <c r="C72" s="6"/>
-      <c r="D72" s="16" t="s">
+      <c r="D72" s="17" t="s">
         <v>7</v>
       </c>
       <c r="E72" s="5"/>
@@ -9237,7 +9476,7 @@
         <v>59</v>
       </c>
       <c r="C73" s="6"/>
-      <c r="D73" s="16" t="s">
+      <c r="D73" s="17" t="s">
         <v>7</v>
       </c>
       <c r="E73" s="5"/>
@@ -9248,7 +9487,7 @@
         <v>60</v>
       </c>
       <c r="C74" s="6"/>
-      <c r="D74" s="16" t="s">
+      <c r="D74" s="17" t="s">
         <v>7</v>
       </c>
       <c r="E74" s="5"/>
@@ -9256,10 +9495,10 @@
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" s="5"/>
       <c r="B75" s="5" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="C75" s="6"/>
-      <c r="D75" s="16" t="s">
+      <c r="D75" s="17" t="s">
         <v>7</v>
       </c>
       <c r="E75" s="7"/>
@@ -9267,10 +9506,10 @@
     <row r="76" ht="18.75" customHeight="1">
       <c r="A76" s="5"/>
       <c r="B76" s="5" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C76" s="6"/>
-      <c r="D76" s="16" t="s">
+      <c r="D76" s="17" t="s">
         <v>7</v>
       </c>
       <c r="E76" s="7"/>
@@ -9339,19 +9578,19 @@
         <v>69</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
     </row>
     <row r="83" ht="18.75" customHeight="1">
       <c r="A83" s="5"/>
       <c r="B83" s="5" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>7</v>
@@ -9371,7 +9610,7 @@
     <row r="85" ht="18.75" customHeight="1">
       <c r="A85" s="5"/>
       <c r="B85" s="5" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>7</v>
@@ -9381,7 +9620,7 @@
     <row r="86" ht="18.75" customHeight="1">
       <c r="A86" s="5"/>
       <c r="B86" s="5" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>7</v>
@@ -9391,7 +9630,7 @@
     <row r="87" ht="18.75" customHeight="1">
       <c r="A87" s="5"/>
       <c r="B87" s="5" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>7</v>
@@ -9400,10 +9639,10 @@
     </row>
     <row r="88" ht="18.75" customHeight="1">
       <c r="A88" s="4" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>7</v>
@@ -9413,7 +9652,7 @@
     <row r="89" ht="18.75" customHeight="1">
       <c r="A89" s="5"/>
       <c r="B89" s="5" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>7</v>
@@ -9423,7 +9662,7 @@
     <row r="90" ht="18.75" customHeight="1">
       <c r="A90" s="5"/>
       <c r="B90" s="5" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>7</v>
@@ -9433,7 +9672,7 @@
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="5"/>
       <c r="B91" s="5" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>7</v>
@@ -9443,7 +9682,7 @@
     <row r="92" ht="18.75" customHeight="1">
       <c r="A92" s="5"/>
       <c r="B92" s="5" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>7</v>
@@ -9453,7 +9692,7 @@
     <row r="93" ht="18.75" customHeight="1">
       <c r="A93" s="5"/>
       <c r="B93" s="5" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>7</v>
@@ -9462,10 +9701,10 @@
     </row>
     <row r="94" ht="18.75" customHeight="1">
       <c r="A94" s="4" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>7</v>
@@ -9475,7 +9714,7 @@
     <row r="95" ht="18.75" customHeight="1">
       <c r="A95" s="5"/>
       <c r="B95" s="5" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>7</v>
@@ -9485,7 +9724,7 @@
     <row r="96" ht="18.75" customHeight="1">
       <c r="A96" s="5"/>
       <c r="B96" s="5" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>7</v>
@@ -9497,7 +9736,7 @@
         <v>71</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="C97" s="6"/>
       <c r="D97" s="6" t="s">
@@ -9518,10 +9757,10 @@
     </row>
     <row r="99" ht="18.75" customHeight="1">
       <c r="A99" s="4" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>7</v>
@@ -9532,7 +9771,7 @@
     <row r="100" ht="18.75" customHeight="1">
       <c r="A100" s="5"/>
       <c r="B100" s="5" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>7</v>
@@ -9543,7 +9782,7 @@
     <row r="101" ht="18.75" customHeight="1">
       <c r="A101" s="5"/>
       <c r="B101" s="5" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>7</v>
@@ -9567,7 +9806,7 @@
     <row r="103" ht="18.75" customHeight="1">
       <c r="A103" s="5"/>
       <c r="B103" s="5" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>7</v>
@@ -9645,10 +9884,10 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="10" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>7</v>
@@ -9659,7 +9898,7 @@
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="13"/>
       <c r="B111" s="11" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="C111" s="12" t="s">
         <v>7</v>
@@ -9670,7 +9909,7 @@
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="13"/>
       <c r="B112" s="11" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="C112" s="12" t="s">
         <v>7</v>
@@ -9680,34 +9919,34 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="10" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="C113" s="12" t="s">
         <v>7</v>
       </c>
       <c r="D113" s="13"/>
-      <c r="E113" s="17"/>
+      <c r="E113" s="18"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="13"/>
       <c r="B114" s="11" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="C114" s="12" t="s">
         <v>7</v>
       </c>
       <c r="D114" s="13"/>
-      <c r="E114" s="17" t="s">
-        <v>153</v>
+      <c r="E114" s="18" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="13"/>
       <c r="B115" s="11" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="C115" s="12" t="s">
         <v>7</v>
@@ -9718,7 +9957,7 @@
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="13"/>
       <c r="B116" s="11" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="C116" s="12" t="s">
         <v>7</v>
@@ -9753,7 +9992,7 @@
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="13"/>
       <c r="B119" s="11" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="C119" s="12" t="s">
         <v>7</v>
@@ -9775,7 +10014,7 @@
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="14" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>7</v>
@@ -9785,10 +10024,10 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="10" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="B122" s="14" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>7</v>
@@ -9799,7 +10038,7 @@
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="14" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>7</v>
@@ -9810,7 +10049,7 @@
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="14" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>7</v>
@@ -9821,7 +10060,7 @@
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="14" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>7</v>
@@ -9832,7 +10071,7 @@
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="14" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>7</v>
@@ -9843,7 +10082,7 @@
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="14" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="C127" s="12" t="s">
         <v>7</v>
@@ -9854,7 +10093,7 @@
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="14" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="C128" s="12" t="s">
         <v>7</v>
@@ -9863,177 +10102,295 @@
       <c r="E128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
-      <c r="C129" s="15"/>
+      <c r="A129" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B129" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D129" s="15"/>
       <c r="E129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
-      <c r="C130" s="15"/>
+      <c r="B130" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D130" s="15"/>
       <c r="E130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
-      <c r="C131" s="15"/>
+      <c r="B131" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D131" s="15"/>
       <c r="E131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
-      <c r="C132" s="15"/>
+      <c r="B132" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D132" s="15"/>
       <c r="E132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="3"/>
-      <c r="B133" s="3"/>
-      <c r="C133" s="15"/>
+      <c r="A133" s="14"/>
+      <c r="B133" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D133" s="15"/>
       <c r="E133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="3"/>
-      <c r="B134" s="3"/>
-      <c r="C134" s="15"/>
+      <c r="A134" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D134" s="15"/>
       <c r="E134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
-      <c r="B135" s="3"/>
-      <c r="C135" s="15"/>
+      <c r="B135" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D135" s="15"/>
       <c r="E135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
-      <c r="B136" s="3"/>
-      <c r="C136" s="15"/>
+      <c r="B136" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D136" s="15"/>
       <c r="E136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
-      <c r="B137" s="3"/>
-      <c r="C137" s="15"/>
+      <c r="B137" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D137" s="15"/>
       <c r="E137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="3"/>
-      <c r="B138" s="3"/>
-      <c r="C138" s="15"/>
+      <c r="A138" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B138" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D138" s="15"/>
       <c r="E138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
-      <c r="B139" s="3"/>
-      <c r="C139" s="15"/>
+      <c r="B139" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D139" s="15"/>
       <c r="E139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
-      <c r="B140" s="3"/>
-      <c r="C140" s="15"/>
+      <c r="B140" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D140" s="15"/>
       <c r="E140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
-      <c r="C141" s="15"/>
+      <c r="A141" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B141" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D141" s="15"/>
       <c r="E141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="15"/>
+      <c r="B142" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D142" s="15"/>
       <c r="E142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
-      <c r="C143" s="15"/>
+      <c r="B143" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D143" s="15"/>
       <c r="E143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
-      <c r="C144" s="15"/>
+      <c r="A144" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B144" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D144" s="15"/>
       <c r="E144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
-      <c r="C145" s="15"/>
+      <c r="B145" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D145" s="15"/>
       <c r="E145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
-      <c r="C146" s="15"/>
+      <c r="A146" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B146" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D146" s="15"/>
       <c r="E146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
-      <c r="C147" s="15"/>
+      <c r="B147" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D147" s="15"/>
       <c r="E147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
-      <c r="C148" s="15"/>
+      <c r="A148" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B148" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D148" s="15"/>
       <c r="E148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
-      <c r="C149" s="15"/>
+      <c r="B149" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D149" s="15"/>
       <c r="E149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
-      <c r="C150" s="15"/>
+      <c r="A150" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B150" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D150" s="15"/>
       <c r="E150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
-      <c r="C151" s="15"/>
+      <c r="B151" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D151" s="15"/>
       <c r="E151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
-      <c r="C152" s="15"/>
+      <c r="A152" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B152" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D152" s="15"/>
       <c r="E152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
-      <c r="C153" s="15"/>
+      <c r="B153" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="D153" s="15"/>
       <c r="E153" s="3"/>
     </row>
@@ -16026,10 +16383,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -16058,10 +16415,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>7</v>
@@ -16071,10 +16428,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>7</v>
@@ -16084,34 +16441,34 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="16"/>
+        <v>205</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="17"/>
       <c r="E4" s="7"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="18"/>
+        <v>206</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="19"/>
       <c r="E5" s="14"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C6" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="15"/>
@@ -16120,9 +16477,9 @@
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>
       <c r="B7" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="15"/>
@@ -16131,9 +16488,9 @@
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="15"/>
@@ -16142,40 +16499,40 @@
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
       <c r="B9" s="14" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="C9" s="15"/>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="19" t="s">
-        <v>179</v>
+      <c r="B10" s="20" t="s">
+        <v>211</v>
       </c>
       <c r="C10" s="15"/>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="20"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="14"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
@@ -22430,117 +22787,117 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="s">
-        <v>182</v>
+      <c r="A1" s="16" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="21" t="s">
-        <v>183</v>
+      <c r="B2" s="16" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="21" t="s">
-        <v>184</v>
+      <c r="B3" s="16" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="21" t="s">
-        <v>185</v>
+      <c r="B4" s="16" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="21" t="s">
-        <v>186</v>
+      <c r="B5" s="16" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="21" t="s">
-        <v>187</v>
+      <c r="B6" s="16" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="21" t="s">
-        <v>188</v>
+      <c r="B7" s="16" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="21" t="s">
-        <v>189</v>
+      <c r="B8" s="16" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="21" t="s">
-        <v>190</v>
+      <c r="B9" s="16" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>161</v>
+      <c r="A11" s="16" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="21" t="s">
-        <v>191</v>
+      <c r="B12" s="16" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="21" t="s">
-        <v>192</v>
+      <c r="B13" s="16" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="21" t="s">
-        <v>193</v>
+      <c r="B14" s="16" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="21" t="s">
-        <v>194</v>
+      <c r="B15" s="16" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="21" t="s">
-        <v>195</v>
+      <c r="B16" s="16" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="21" t="s">
-        <v>196</v>
+      <c r="B17" s="16" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="21" t="s">
-        <v>197</v>
+      <c r="B18" s="16" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="21" t="s">
-        <v>198</v>
+      <c r="B19" s="16" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="21" t="s">
-        <v>199</v>
+      <c r="B20" s="16" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="21" t="s">
-        <v>200</v>
+      <c r="B21" s="16" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="21" t="s">
-        <v>201</v>
+      <c r="B22" s="16" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="21" t="s">
-        <v>202</v>
+      <c r="B23" s="16" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21"/>
+      <c r="A25" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -22558,58 +22915,83 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="s">
-        <v>203</v>
+      <c r="A2" s="16" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="s">
-        <v>204</v>
+      <c r="A3" s="16" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="s">
-        <v>205</v>
+      <c r="A4" s="16" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>206</v>
+      <c r="A5" s="16" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="s">
-        <v>207</v>
+      <c r="A6" s="16" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>208</v>
+      <c r="A7" s="16" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="s">
-        <v>209</v>
+      <c r="A8" s="16" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>210</v>
+      <c r="A9" s="16" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="s">
-        <v>211</v>
+      <c r="A10" s="16" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>212</v>
+      <c r="A11" s="16" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
